--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260820.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260820.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>913,037,000</t>
+          <t>177,011,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.74%</t>
+          <t>9.56%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>177,011,000</t>
+          <t>913,037,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.63%</t>
+          <t>9.56%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.90%</t>
+          <t>5.86%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>4.44%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>3.58%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
@@ -946,117 +946,117 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>83,020,000</t>
+          <t>98,298,442</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>98,298,442</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>83,020,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>236,458,056</t>
+          <t>145,204,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>145,204,000</t>
+          <t>236,458,056</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -1100,46 +1100,46 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>35,510,000</t>
+          <t>1,488</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>188,603,000</t>
+          <t>35,510,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,22 +1151,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,364</t>
+          <t>188,603,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>13,241,000</t>
+          <t>12,686,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>26,442,630,565</t>
+          <t>27,591,337,309</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,616,516,894</t>
+          <t>4,729,914,305</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-11,451,545</t>
+          <t>-72,636,247</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
